--- a/plugins/foreign-trade-customer-development/skills/foreign-trade-customer-development/assets/prospect-development-workbook.xlsx
+++ b/plugins/foreign-trade-customer-development/skills/foreign-trade-customer-development/assets/prospect-development-workbook.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户总览" sheetId="1" r:id="R755619076f0d49e0"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公司研究" sheetId="2" r:id="Raf0989ae00b64082"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目机会" sheetId="3" r:id="R3ec2b8c295314302"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="联系人" sheetId="4" r:id="R83c8bbec9eaf4f7d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据来源" sheetId="5" r:id="R73677259106445b6"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="海关与贸易" sheetId="6" r:id="R48e56727baea425a"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险核验" sheetId="7" r:id="Rfe690898bf764a09"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="触达记录" sheetId="8" r:id="R8717178180734492"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="移交记录" sheetId="9" r:id="Rd098b0f927f648bd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户总览" sheetId="1" r:id="R4d310c9411314a4b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公司研究" sheetId="2" r:id="R74919e9813104650"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目机会" sheetId="3" r:id="R6ae4c5957e8f4324"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="联系人" sheetId="4" r:id="R4f6906fa16214011"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据来源" sheetId="5" r:id="R24a0360e295c45f1"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="海关与贸易" sheetId="6" r:id="Ra522610293a845c8"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险核验" sheetId="7" r:id="R53521b663cef4c6d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="触达记录" sheetId="8" r:id="R93842d13b5db42e7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="移交记录" sheetId="9" r:id="R4bc58eef2c4d4650"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,7 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="3">
+  <x:fonts count="5">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -38,13 +38,45 @@
       <x:color rgb="FF17365D"/>
       <x:name val="Carlito"/>
     </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF17365D"/>
+      <x:name val="Carlito"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="4">
+  <x:fills count="8">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="gray125"/>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF17365D"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
     </x:fill>
     <x:fill>
       <x:patternFill patternType="solid">
@@ -91,7 +123,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="13">
+  <x:cellXfs count="29">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -115,6 +147,42 @@
       <x:alignment horizontal="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -464,7 +532,7 @@
       <x:formula1>"资料充分且一致,整体可信但存在缺口,存在重大冲突需要核验,证据不足无法判断"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="J3:J5000">
-      <x:formula1>"未触发,待核验,业务员批准继续,已关闭"</x:formula1>
+      <x:formula1>"未触发,待核验,暂停待业务员审核,业务员批准继续,已关闭"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="Q3:Q5000">
       <x:formula1>"未触发,触达已暂停,待邮件助手,已移交,业务员已决定"</x:formula1>
@@ -691,6 +759,10 @@
     <x:col min="13" max="13" width="28" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="15" hidden="0" customWidth="1"/>
     <x:col min="15" max="15" width="23" hidden="0" customWidth="1"/>
+    <x:col min="16" max="16" width="23" hidden="0" customWidth="1"/>
+    <x:col min="17" max="17" width="22" hidden="0" customWidth="1"/>
+    <x:col min="18" max="18" width="31" hidden="0" customWidth="1"/>
+    <x:col min="19" max="19" width="36" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
@@ -739,6 +811,18 @@
       <x:c r="O1" s="6" t="str">
         <x:v>salesperson_approval</x:v>
       </x:c>
+      <x:c r="P1" s="26" t="str">
+        <x:v>employer_or_entity</x:v>
+      </x:c>
+      <x:c r="Q1" s="26" t="str">
+        <x:v>entity_match_basis</x:v>
+      </x:c>
+      <x:c r="R1" s="26" t="str">
+        <x:v>contact_source_reference</x:v>
+      </x:c>
+      <x:c r="S1" s="26" t="str">
+        <x:v>uncertainty_note</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="12" t="str">
@@ -786,9 +870,21 @@
       <x:c r="O2" s="12" t="str">
         <x:v>业务员批准状态</x:v>
       </x:c>
+      <x:c r="P2" s="28" t="str">
+        <x:v>所属公司或主体</x:v>
+      </x:c>
+      <x:c r="Q2" s="28" t="str">
+        <x:v>主体匹配依据</x:v>
+      </x:c>
+      <x:c r="R2" s="28" t="str">
+        <x:v>联系信息来源或职业页面</x:v>
+      </x:c>
+      <x:c r="S2" s="28" t="str">
+        <x:v>身份职位或联系方式不确定项</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A2:O2"/>
+  <x:autoFilter ref="A2:S2"/>
   <x:dataValidations count="1">
     <x:dataValidation type="list" sqref="K3:K5000">
       <x:formula1>"正常使用,限制使用,隔离待核实"</x:formula1>
@@ -816,6 +912,7 @@
     <x:col min="12" max="12" width="17" hidden="0" customWidth="1"/>
     <x:col min="13" max="13" width="15" hidden="0" customWidth="1"/>
     <x:col min="14" max="14" width="28" hidden="0" customWidth="1"/>
+    <x:col min="15" max="15" width="32" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="36" customHeight="1">
@@ -861,6 +958,9 @@
       <x:c r="N1" s="6" t="str">
         <x:v>conflict_note</x:v>
       </x:c>
+      <x:c r="O1" s="26" t="str">
+        <x:v>source_region_or_jurisdiction</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
       <x:c r="A2" s="12" t="str">
@@ -905,9 +1005,12 @@
       <x:c r="N2" s="12" t="str">
         <x:v>冲突说明</x:v>
       </x:c>
+      <x:c r="O2" s="28" t="str">
+        <x:v>来源适用地区或管辖范围</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
-  <x:autoFilter ref="A2:N2"/>
+  <x:autoFilter ref="A2:O2"/>
   <x:dataValidations count="1">
     <x:dataValidation type="list" sqref="L3:L5000">
       <x:formula1>"官方直接证据,多来源相互印证,单一来源待验证,合理推断,来源相互冲突,信息已经过期,来源不明隔离待核实"</x:formula1>
@@ -1223,7 +1326,7 @@
       <x:formula1>"官方直接证据,多来源相互印证,单一来源待验证,合理推断,来源相互冲突,信息已经过期,来源不明隔离待核实"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="M3:M5000">
-      <x:formula1>"未触发,待核验,业务员批准继续,已关闭"</x:formula1>
+      <x:formula1>"未触发,待核验,暂停待业务员审核,业务员批准继续,已关闭"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1447,7 +1550,7 @@
   <x:autoFilter ref="A2:L2"/>
   <x:dataValidations count="2">
     <x:dataValidation type="list" sqref="H3:H5000">
-      <x:formula1>"未触发,待核验,业务员批准继续,已关闭"</x:formula1>
+      <x:formula1>"未触发,待核验,暂停待业务员审核,业务员批准继续,已关闭"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="J3:J5000">
       <x:formula1>"未触发,触达已暂停,待邮件助手,已移交,业务员已决定"</x:formula1>

--- a/plugins/foreign-trade-customer-development/skills/foreign-trade-customer-development/assets/prospect-development-workbook.xlsx
+++ b/plugins/foreign-trade-customer-development/skills/foreign-trade-customer-development/assets/prospect-development-workbook.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户总览" sheetId="1" r:id="R4d310c9411314a4b"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公司研究" sheetId="2" r:id="R74919e9813104650"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目机会" sheetId="3" r:id="R6ae4c5957e8f4324"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="联系人" sheetId="4" r:id="R4f6906fa16214011"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据来源" sheetId="5" r:id="R24a0360e295c45f1"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="海关与贸易" sheetId="6" r:id="Ra522610293a845c8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险核验" sheetId="7" r:id="R53521b663cef4c6d"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="触达记录" sheetId="8" r:id="R93842d13b5db42e7"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="移交记录" sheetId="9" r:id="R4bc58eef2c4d4650"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户总览" sheetId="1" r:id="R9d7c00ac1cbf469e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公司研究" sheetId="2" r:id="R2b21b8ea0a1d4911"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目机会" sheetId="3" r:id="R7c7e681b53444fe4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="联系人" sheetId="4" r:id="R892d8cfe81d54e4e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据来源" sheetId="5" r:id="Rfeffafa33a854df3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="海关与贸易" sheetId="6" r:id="R0693413d5afb437c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险核验" sheetId="7" r:id="Rdf7224406dce4d30"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="触达记录" sheetId="8" r:id="Rd8d122d6ff7d4243"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="移交记录" sheetId="9" r:id="Rcd2c4ada5c684618"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -522,19 +522,19 @@
   </x:sheetData>
   <x:autoFilter ref="A2:R2"/>
   <x:dataValidations count="5">
-    <x:dataValidation type="list" sqref="G3:G5000">
+    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="G3:G5000">
       <x:formula1>"待业务员筛选,已确认,已暂停,已关闭"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="H3:H5000">
+    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="H3:H5000">
       <x:formula1>"不继续,普通候选,潜力客户"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="I3:I5000">
+    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="I3:I5000">
       <x:formula1>"资料充分且一致,整体可信但存在缺口,存在重大冲突需要核验,证据不足无法判断"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="J3:J5000">
+    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="J3:J5000">
       <x:formula1>"未触发,待核验,暂停待业务员审核,业务员批准继续,已关闭"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="Q3:Q5000">
+    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="Q3:Q5000">
       <x:formula1>"未触发,触达已暂停,待邮件助手,已移交,业务员已决定"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -639,7 +639,7 @@
   </x:sheetData>
   <x:autoFilter ref="A2:L2"/>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="H3:H5000">
+    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="H3:H5000">
       <x:formula1>"官方直接证据,多来源相互印证,单一来源待验证,合理推断,来源相互冲突,信息已经过期,来源不明隔离待核实"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -886,7 +886,7 @@
   </x:sheetData>
   <x:autoFilter ref="A2:S2"/>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="K3:K5000">
+    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="K3:K5000">
       <x:formula1>"正常使用,限制使用,隔离待核实"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -1012,7 +1012,7 @@
   </x:sheetData>
   <x:autoFilter ref="A2:O2"/>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="L3:L5000">
+    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="L3:L5000">
       <x:formula1>"官方直接证据,多来源相互印证,单一来源待验证,合理推断,来源相互冲突,信息已经过期,来源不明隔离待核实"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -1322,10 +1322,10 @@
   </x:sheetData>
   <x:autoFilter ref="A2:O2"/>
   <x:dataValidations count="2">
-    <x:dataValidation type="list" sqref="K3:K5000">
+    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="K3:K5000">
       <x:formula1>"官方直接证据,多来源相互印证,单一来源待验证,合理推断,来源相互冲突,信息已经过期,来源不明隔离待核实"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="M3:M5000">
+    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="M3:M5000">
       <x:formula1>"未触发,待核验,暂停待业务员审核,业务员批准继续,已关闭"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -1444,7 +1444,7 @@
   </x:sheetData>
   <x:autoFilter ref="A2:N2"/>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" sqref="F3:F5000">
+    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="F3:F5000">
       <x:formula1>"草稿,业务员批准,计划触达,实际发送,实际回复"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -1549,10 +1549,10 @@
   </x:sheetData>
   <x:autoFilter ref="A2:L2"/>
   <x:dataValidations count="2">
-    <x:dataValidation type="list" sqref="H3:H5000">
+    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="H3:H5000">
       <x:formula1>"未触发,待核验,暂停待业务员审核,业务员批准继续,已关闭"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" sqref="J3:J5000">
+    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="J3:J5000">
       <x:formula1>"未触发,触达已暂停,待邮件助手,已移交,业务员已决定"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>

--- a/plugins/foreign-trade-customer-development/skills/foreign-trade-customer-development/assets/prospect-development-workbook.xlsx
+++ b/plugins/foreign-trade-customer-development/skills/foreign-trade-customer-development/assets/prospect-development-workbook.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户总览" sheetId="1" r:id="R9d7c00ac1cbf469e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公司研究" sheetId="2" r:id="R2b21b8ea0a1d4911"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目机会" sheetId="3" r:id="R7c7e681b53444fe4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="联系人" sheetId="4" r:id="R892d8cfe81d54e4e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据来源" sheetId="5" r:id="Rfeffafa33a854df3"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="海关与贸易" sheetId="6" r:id="R0693413d5afb437c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险核验" sheetId="7" r:id="Rdf7224406dce4d30"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="触达记录" sheetId="8" r:id="Rd8d122d6ff7d4243"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="移交记录" sheetId="9" r:id="Rcd2c4ada5c684618"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户总览" sheetId="1" r:id="Rc740c257dbfb40ed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公司研究" sheetId="2" r:id="R155667a47a8f46c4"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目机会" sheetId="3" r:id="R69f43e9875874f69"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="联系人" sheetId="4" r:id="R616772a7b3674eb5"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据来源" sheetId="5" r:id="R560dc70752974c38"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="海关与贸易" sheetId="6" r:id="Rbc2def0c212b47da"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险核验" sheetId="7" r:id="Re4a425e2910a4816"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="触达记录" sheetId="8" r:id="Raed06d9391384839"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="移交记录" sheetId="9" r:id="R0569bd6285f94d7e"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -522,19 +522,19 @@
   </x:sheetData>
   <x:autoFilter ref="A2:R2"/>
   <x:dataValidations count="5">
-    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="G3:G5000">
+    <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="G3:G5000">
       <x:formula1>"待业务员筛选,已确认,已暂停,已关闭"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="H3:H5000">
+    <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="H3:H5000">
       <x:formula1>"不继续,普通候选,潜力客户"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="I3:I5000">
+    <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="I3:I5000">
       <x:formula1>"资料充分且一致,整体可信但存在缺口,存在重大冲突需要核验,证据不足无法判断"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="J3:J5000">
+    <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="J3:J5000">
       <x:formula1>"未触发,待核验,暂停待业务员审核,业务员批准继续,已关闭"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="Q3:Q5000">
+    <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="Q3:Q5000">
       <x:formula1>"未触发,触达已暂停,待邮件助手,已移交,业务员已决定"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -639,7 +639,7 @@
   </x:sheetData>
   <x:autoFilter ref="A2:L2"/>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="H3:H5000">
+    <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="H3:H5000">
       <x:formula1>"官方直接证据,多来源相互印证,单一来源待验证,合理推断,来源相互冲突,信息已经过期,来源不明隔离待核实"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -886,7 +886,7 @@
   </x:sheetData>
   <x:autoFilter ref="A2:S2"/>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="K3:K5000">
+    <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="K3:K5000">
       <x:formula1>"正常使用,限制使用,隔离待核实"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -1012,7 +1012,7 @@
   </x:sheetData>
   <x:autoFilter ref="A2:O2"/>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="L3:L5000">
+    <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="L3:L5000">
       <x:formula1>"官方直接证据,多来源相互印证,单一来源待验证,合理推断,来源相互冲突,信息已经过期,来源不明隔离待核实"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -1322,10 +1322,10 @@
   </x:sheetData>
   <x:autoFilter ref="A2:O2"/>
   <x:dataValidations count="2">
-    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="K3:K5000">
+    <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="K3:K5000">
       <x:formula1>"官方直接证据,多来源相互印证,单一来源待验证,合理推断,来源相互冲突,信息已经过期,来源不明隔离待核实"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="M3:M5000">
+    <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="M3:M5000">
       <x:formula1>"未触发,待核验,暂停待业务员审核,业务员批准继续,已关闭"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -1444,7 +1444,7 @@
   </x:sheetData>
   <x:autoFilter ref="A2:N2"/>
   <x:dataValidations count="1">
-    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="F3:F5000">
+    <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="F3:F5000">
       <x:formula1>"草稿,业务员批准,计划触达,实际发送,实际回复"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
@@ -1549,10 +1549,10 @@
   </x:sheetData>
   <x:autoFilter ref="A2:L2"/>
   <x:dataValidations count="2">
-    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="H3:H5000">
+    <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="H3:H5000">
       <x:formula1>"未触发,待核验,暂停待业务员审核,业务员批准继续,已关闭"</x:formula1>
     </x:dataValidation>
-    <x:dataValidation type="list" errorStyle="stop" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="J3:J5000">
+    <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="J3:J5000">
       <x:formula1>"未触发,触达已暂停,待邮件助手,已移交,业务员已决定"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>

--- a/plugins/foreign-trade-customer-development/skills/foreign-trade-customer-development/assets/prospect-development-workbook.xlsx
+++ b/plugins/foreign-trade-customer-development/skills/foreign-trade-customer-development/assets/prospect-development-workbook.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户总览" sheetId="1" r:id="Rc740c257dbfb40ed"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公司研究" sheetId="2" r:id="R155667a47a8f46c4"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目机会" sheetId="3" r:id="R69f43e9875874f69"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="联系人" sheetId="4" r:id="R616772a7b3674eb5"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据来源" sheetId="5" r:id="R560dc70752974c38"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="海关与贸易" sheetId="6" r:id="Rbc2def0c212b47da"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险核验" sheetId="7" r:id="Re4a425e2910a4816"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="触达记录" sheetId="8" r:id="Raed06d9391384839"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="移交记录" sheetId="9" r:id="R0569bd6285f94d7e"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="客户总览" sheetId="1" r:id="R855ba0bb502a4f50"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="公司研究" sheetId="2" r:id="R0eacfc3bd5a74f51"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="项目机会" sheetId="3" r:id="Rf66855204e764a18"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="联系人" sheetId="4" r:id="R7eb95ef45e9848d3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="证据来源" sheetId="5" r:id="Rf584a61770a546aa"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="海关与贸易" sheetId="6" r:id="Rb4c287c3ca534bcc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="风险核验" sheetId="7" r:id="R2af746f92a614d20"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="触达记录" sheetId="8" r:id="Rec57c9f46c0e437b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="移交记录" sheetId="9" r:id="R21e582d5edcd49db"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -21,7 +21,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:fonts count="5">
+  <x:fonts count="6">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -49,6 +49,12 @@
       <x:sz val="11"/>
       <x:color rgb="FF17365D"/>
       <x:name val="Carlito"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="10"/>
+      <x:color rgb="FF17365D"/>
+      <x:name val="Arial Unicode MS"/>
     </x:font>
   </x:fonts>
   <x:fills count="8">
@@ -123,7 +129,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="29">
+  <x:cellXfs count="30">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -183,6 +189,9 @@
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
     <x:xf numFmtId="0" fontId="2" fillId="7" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
@@ -464,58 +473,58 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
-      <x:c r="A2" s="12" t="str">
+      <x:c r="A2" s="29" t="str">
         <x:v>客户编号</x:v>
       </x:c>
-      <x:c r="B2" s="12" t="str">
+      <x:c r="B2" s="29" t="str">
         <x:v>公司常用名称</x:v>
       </x:c>
-      <x:c r="C2" s="12" t="str">
+      <x:c r="C2" s="29" t="str">
         <x:v>法定注册名称</x:v>
       </x:c>
-      <x:c r="D2" s="12" t="str">
+      <x:c r="D2" s="29" t="str">
         <x:v>公司网站</x:v>
       </x:c>
-      <x:c r="E2" s="12" t="str">
+      <x:c r="E2" s="29" t="str">
         <x:v>国家或地区</x:v>
       </x:c>
-      <x:c r="F2" s="12" t="str">
+      <x:c r="F2" s="29" t="str">
         <x:v>商业模式</x:v>
       </x:c>
-      <x:c r="G2" s="12" t="str">
+      <x:c r="G2" s="29" t="str">
         <x:v>筛选状态</x:v>
       </x:c>
-      <x:c r="H2" s="12" t="str">
+      <x:c r="H2" s="29" t="str">
         <x:v>业务员客户分类</x:v>
       </x:c>
-      <x:c r="I2" s="12" t="str">
+      <x:c r="I2" s="29" t="str">
         <x:v>信息可靠性</x:v>
       </x:c>
-      <x:c r="J2" s="12" t="str">
+      <x:c r="J2" s="29" t="str">
         <x:v>风险门状态</x:v>
       </x:c>
-      <x:c r="K2" s="12" t="str">
+      <x:c r="K2" s="29" t="str">
         <x:v>推荐机会编号</x:v>
       </x:c>
-      <x:c r="L2" s="12" t="str">
+      <x:c r="L2" s="29" t="str">
         <x:v>主要联系人编号</x:v>
       </x:c>
-      <x:c r="M2" s="12" t="str">
+      <x:c r="M2" s="29" t="str">
         <x:v>最近研究日期</x:v>
       </x:c>
-      <x:c r="N2" s="12" t="str">
+      <x:c r="N2" s="29" t="str">
         <x:v>最近触达日期</x:v>
       </x:c>
-      <x:c r="O2" s="12" t="str">
+      <x:c r="O2" s="29" t="str">
         <x:v>下一步行动</x:v>
       </x:c>
-      <x:c r="P2" s="12" t="str">
+      <x:c r="P2" s="29" t="str">
         <x:v>下一步行动日期</x:v>
       </x:c>
-      <x:c r="Q2" s="12" t="str">
+      <x:c r="Q2" s="29" t="str">
         <x:v>移交状态</x:v>
       </x:c>
-      <x:c r="R2" s="12" t="str">
+      <x:c r="R2" s="29" t="str">
         <x:v>业务员备注</x:v>
       </x:c>
     </x:row>
@@ -535,7 +544,7 @@
       <x:formula1>"未触发,待核验,暂停待业务员审核,业务员批准继续,已关闭"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="Q3:Q5000">
-      <x:formula1>"未触发,触达已暂停,待邮件助手,已移交,业务员已决定"</x:formula1>
+      <x:formula1>"未触发,待邮件助手,已移交,业务员已决定"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -599,40 +608,40 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
-      <x:c r="A2" s="12" t="str">
+      <x:c r="A2" s="29" t="str">
         <x:v>研究记录编号</x:v>
       </x:c>
-      <x:c r="B2" s="12" t="str">
+      <x:c r="B2" s="29" t="str">
         <x:v>客户编号</x:v>
       </x:c>
-      <x:c r="C2" s="12" t="str">
+      <x:c r="C2" s="29" t="str">
         <x:v>研究层级</x:v>
       </x:c>
-      <x:c r="D2" s="12" t="str">
+      <x:c r="D2" s="29" t="str">
         <x:v>研究章节</x:v>
       </x:c>
-      <x:c r="E2" s="12" t="str">
+      <x:c r="E2" s="29" t="str">
         <x:v>原文研究发现</x:v>
       </x:c>
-      <x:c r="F2" s="12" t="str">
+      <x:c r="F2" s="29" t="str">
         <x:v>研究发现中文摘要</x:v>
       </x:c>
-      <x:c r="G2" s="12" t="str">
+      <x:c r="G2" s="29" t="str">
         <x:v>证据编号</x:v>
       </x:c>
-      <x:c r="H2" s="12" t="str">
+      <x:c r="H2" s="29" t="str">
         <x:v>证据状态</x:v>
       </x:c>
-      <x:c r="I2" s="12" t="str">
+      <x:c r="I2" s="29" t="str">
         <x:v>来源发布日期</x:v>
       </x:c>
-      <x:c r="J2" s="12" t="str">
+      <x:c r="J2" s="29" t="str">
         <x:v>观察记录时间</x:v>
       </x:c>
-      <x:c r="K2" s="12" t="str">
+      <x:c r="K2" s="29" t="str">
         <x:v>信息缺口或冲突</x:v>
       </x:c>
-      <x:c r="L2" s="12" t="str">
+      <x:c r="L2" s="29" t="str">
         <x:v>业务员确认状态</x:v>
       </x:c>
     </x:row>
@@ -700,37 +709,37 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
-      <x:c r="A2" s="12" t="str">
+      <x:c r="A2" s="29" t="str">
         <x:v>机会编号</x:v>
       </x:c>
-      <x:c r="B2" s="12" t="str">
+      <x:c r="B2" s="29" t="str">
         <x:v>客户编号</x:v>
       </x:c>
-      <x:c r="C2" s="12" t="str">
+      <x:c r="C2" s="29" t="str">
         <x:v>已确认客户事实</x:v>
       </x:c>
-      <x:c r="D2" s="12" t="str">
+      <x:c r="D2" s="29" t="str">
         <x:v>应用或采购场景</x:v>
       </x:c>
-      <x:c r="E2" s="12" t="str">
+      <x:c r="E2" s="29" t="str">
         <x:v>已批准产品引用</x:v>
       </x:c>
-      <x:c r="F2" s="12" t="str">
+      <x:c r="F2" s="29" t="str">
         <x:v>匹配依据</x:v>
       </x:c>
-      <x:c r="G2" s="12" t="str">
+      <x:c r="G2" s="29" t="str">
         <x:v>待验证问题</x:v>
       </x:c>
-      <x:c r="H2" s="12" t="str">
+      <x:c r="H2" s="29" t="str">
         <x:v>主要联系人编号</x:v>
       </x:c>
-      <x:c r="I2" s="12" t="str">
+      <x:c r="I2" s="29" t="str">
         <x:v>推荐状态</x:v>
       </x:c>
-      <x:c r="J2" s="12" t="str">
+      <x:c r="J2" s="29" t="str">
         <x:v>业务员决定</x:v>
       </x:c>
-      <x:c r="K2" s="12" t="str">
+      <x:c r="K2" s="29" t="str">
         <x:v>决定日期</x:v>
       </x:c>
     </x:row>
@@ -825,61 +834,61 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
-      <x:c r="A2" s="12" t="str">
+      <x:c r="A2" s="29" t="str">
         <x:v>联系人编号</x:v>
       </x:c>
-      <x:c r="B2" s="12" t="str">
+      <x:c r="B2" s="29" t="str">
         <x:v>客户编号</x:v>
       </x:c>
-      <x:c r="C2" s="12" t="str">
+      <x:c r="C2" s="29" t="str">
         <x:v>联系人姓名</x:v>
       </x:c>
-      <x:c r="D2" s="12" t="str">
+      <x:c r="D2" s="29" t="str">
         <x:v>职务名称</x:v>
       </x:c>
-      <x:c r="E2" s="12" t="str">
+      <x:c r="E2" s="29" t="str">
         <x:v>可能承担的角色</x:v>
       </x:c>
-      <x:c r="F2" s="12" t="str">
+      <x:c r="F2" s="29" t="str">
         <x:v>角色证据编号</x:v>
       </x:c>
-      <x:c r="G2" s="12" t="str">
+      <x:c r="G2" s="29" t="str">
         <x:v>联系渠道</x:v>
       </x:c>
-      <x:c r="H2" s="12" t="str">
+      <x:c r="H2" s="29" t="str">
         <x:v>联系方式内容</x:v>
       </x:c>
-      <x:c r="I2" s="12" t="str">
+      <x:c r="I2" s="29" t="str">
         <x:v>真实性状态</x:v>
       </x:c>
-      <x:c r="J2" s="12" t="str">
+      <x:c r="J2" s="29" t="str">
         <x:v>来源可靠性</x:v>
       </x:c>
-      <x:c r="K2" s="12" t="str">
+      <x:c r="K2" s="29" t="str">
         <x:v>使用许可</x:v>
       </x:c>
-      <x:c r="L2" s="12" t="str">
+      <x:c r="L2" s="29" t="str">
         <x:v>联系顺序</x:v>
       </x:c>
-      <x:c r="M2" s="12" t="str">
+      <x:c r="M2" s="29" t="str">
         <x:v>排序依据</x:v>
       </x:c>
-      <x:c r="N2" s="12" t="str">
+      <x:c r="N2" s="29" t="str">
         <x:v>观察记录时间</x:v>
       </x:c>
-      <x:c r="O2" s="12" t="str">
+      <x:c r="O2" s="29" t="str">
         <x:v>业务员批准状态</x:v>
       </x:c>
-      <x:c r="P2" s="28" t="str">
+      <x:c r="P2" s="29" t="str">
         <x:v>所属公司或主体</x:v>
       </x:c>
-      <x:c r="Q2" s="28" t="str">
+      <x:c r="Q2" s="29" t="str">
         <x:v>主体匹配依据</x:v>
       </x:c>
-      <x:c r="R2" s="28" t="str">
+      <x:c r="R2" s="29" t="str">
         <x:v>联系信息来源或职业页面</x:v>
       </x:c>
-      <x:c r="S2" s="28" t="str">
+      <x:c r="S2" s="29" t="str">
         <x:v>身份职位或联系方式不确定项</x:v>
       </x:c>
     </x:row>
@@ -963,49 +972,49 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
-      <x:c r="A2" s="12" t="str">
+      <x:c r="A2" s="29" t="str">
         <x:v>证据编号</x:v>
       </x:c>
-      <x:c r="B2" s="12" t="str">
+      <x:c r="B2" s="29" t="str">
         <x:v>客户编号</x:v>
       </x:c>
-      <x:c r="C2" s="12" t="str">
+      <x:c r="C2" s="29" t="str">
         <x:v>来源类型</x:v>
       </x:c>
-      <x:c r="D2" s="12" t="str">
+      <x:c r="D2" s="29" t="str">
         <x:v>来源标题</x:v>
       </x:c>
-      <x:c r="E2" s="12" t="str">
+      <x:c r="E2" s="29" t="str">
         <x:v>来源网址或本地引用</x:v>
       </x:c>
-      <x:c r="F2" s="12" t="str">
+      <x:c r="F2" s="29" t="str">
         <x:v>来源主体</x:v>
       </x:c>
-      <x:c r="G2" s="12" t="str">
+      <x:c r="G2" s="29" t="str">
         <x:v>来源语言</x:v>
       </x:c>
-      <x:c r="H2" s="12" t="str">
+      <x:c r="H2" s="29" t="str">
         <x:v>原文摘录</x:v>
       </x:c>
-      <x:c r="I2" s="12" t="str">
+      <x:c r="I2" s="29" t="str">
         <x:v>中文摘要</x:v>
       </x:c>
-      <x:c r="J2" s="12" t="str">
+      <x:c r="J2" s="29" t="str">
         <x:v>来源发布日期</x:v>
       </x:c>
-      <x:c r="K2" s="12" t="str">
+      <x:c r="K2" s="29" t="str">
         <x:v>观察记录时间</x:v>
       </x:c>
-      <x:c r="L2" s="12" t="str">
+      <x:c r="L2" s="29" t="str">
         <x:v>证据状态</x:v>
       </x:c>
-      <x:c r="M2" s="12" t="str">
+      <x:c r="M2" s="29" t="str">
         <x:v>访问范围</x:v>
       </x:c>
-      <x:c r="N2" s="12" t="str">
+      <x:c r="N2" s="29" t="str">
         <x:v>冲突说明</x:v>
       </x:c>
-      <x:c r="O2" s="28" t="str">
+      <x:c r="O2" s="29" t="str">
         <x:v>来源适用地区或管辖范围</x:v>
       </x:c>
     </x:row>
@@ -1125,76 +1134,76 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
-      <x:c r="A2" s="12" t="str">
+      <x:c r="A2" s="29" t="str">
         <x:v>贸易记录编号</x:v>
       </x:c>
-      <x:c r="B2" s="12" t="str">
+      <x:c r="B2" s="29" t="str">
         <x:v>客户编号</x:v>
       </x:c>
-      <x:c r="C2" s="12" t="str">
+      <x:c r="C2" s="29" t="str">
         <x:v>数据来源</x:v>
       </x:c>
-      <x:c r="D2" s="12" t="str">
+      <x:c r="D2" s="29" t="str">
         <x:v>访问范围</x:v>
       </x:c>
-      <x:c r="E2" s="12" t="str">
+      <x:c r="E2" s="29" t="str">
         <x:v>覆盖国家或地区</x:v>
       </x:c>
-      <x:c r="F2" s="12" t="str">
+      <x:c r="F2" s="29" t="str">
         <x:v>覆盖期间</x:v>
       </x:c>
-      <x:c r="G2" s="12" t="str">
+      <x:c r="G2" s="29" t="str">
         <x:v>观察到的企业名称</x:v>
       </x:c>
-      <x:c r="H2" s="12" t="str">
+      <x:c r="H2" s="29" t="str">
         <x:v>观察到的企业地址</x:v>
       </x:c>
-      <x:c r="I2" s="12" t="str">
+      <x:c r="I2" s="29" t="str">
         <x:v>主体匹配依据</x:v>
       </x:c>
-      <x:c r="J2" s="12" t="str">
+      <x:c r="J2" s="29" t="str">
         <x:v>贸易方向</x:v>
       </x:c>
-      <x:c r="K2" s="12" t="str">
+      <x:c r="K2" s="29" t="str">
         <x:v>货运期间</x:v>
       </x:c>
-      <x:c r="L2" s="12" t="str">
+      <x:c r="L2" s="29" t="str">
         <x:v>可见交易频次</x:v>
       </x:c>
-      <x:c r="M2" s="12" t="str">
+      <x:c r="M2" s="29" t="str">
         <x:v>产品描述</x:v>
       </x:c>
-      <x:c r="N2" s="12" t="str">
+      <x:c r="N2" s="29" t="str">
         <x:v>海关编码</x:v>
       </x:c>
-      <x:c r="O2" s="12" t="str">
+      <x:c r="O2" s="29" t="str">
         <x:v>数量</x:v>
       </x:c>
-      <x:c r="P2" s="12" t="str">
+      <x:c r="P2" s="29" t="str">
         <x:v>数量单位</x:v>
       </x:c>
-      <x:c r="Q2" s="12" t="str">
+      <x:c r="Q2" s="29" t="str">
         <x:v>重量</x:v>
       </x:c>
-      <x:c r="R2" s="12" t="str">
+      <x:c r="R2" s="29" t="str">
         <x:v>重量单位</x:v>
       </x:c>
-      <x:c r="S2" s="12" t="str">
+      <x:c r="S2" s="29" t="str">
         <x:v>申报价值</x:v>
       </x:c>
-      <x:c r="T2" s="12" t="str">
+      <x:c r="T2" s="29" t="str">
         <x:v>申报币种</x:v>
       </x:c>
-      <x:c r="U2" s="12" t="str">
+      <x:c r="U2" s="29" t="str">
         <x:v>贸易伙伴或国家</x:v>
       </x:c>
-      <x:c r="V2" s="12" t="str">
+      <x:c r="V2" s="29" t="str">
         <x:v>数据局限说明</x:v>
       </x:c>
-      <x:c r="W2" s="12" t="str">
+      <x:c r="W2" s="29" t="str">
         <x:v>观察记录时间</x:v>
       </x:c>
-      <x:c r="X2" s="12" t="str">
+      <x:c r="X2" s="29" t="str">
         <x:v>证据编号</x:v>
       </x:c>
     </x:row>
@@ -1273,49 +1282,49 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
-      <x:c r="A2" s="12" t="str">
+      <x:c r="A2" s="29" t="str">
         <x:v>风险记录编号</x:v>
       </x:c>
-      <x:c r="B2" s="12" t="str">
+      <x:c r="B2" s="29" t="str">
         <x:v>客户编号</x:v>
       </x:c>
-      <x:c r="C2" s="12" t="str">
+      <x:c r="C2" s="29" t="str">
         <x:v>风险类型</x:v>
       </x:c>
-      <x:c r="D2" s="12" t="str">
+      <x:c r="D2" s="29" t="str">
         <x:v>匹配到的主体</x:v>
       </x:c>
-      <x:c r="E2" s="12" t="str">
+      <x:c r="E2" s="29" t="str">
         <x:v>主体匹配依据</x:v>
       </x:c>
-      <x:c r="F2" s="12" t="str">
+      <x:c r="F2" s="29" t="str">
         <x:v>指控或记录内容</x:v>
       </x:c>
-      <x:c r="G2" s="12" t="str">
+      <x:c r="G2" s="29" t="str">
         <x:v>证据编号</x:v>
       </x:c>
-      <x:c r="H2" s="12" t="str">
+      <x:c r="H2" s="29" t="str">
         <x:v>管辖地区</x:v>
       </x:c>
-      <x:c r="I2" s="12" t="str">
+      <x:c r="I2" s="29" t="str">
         <x:v>记录日期</x:v>
       </x:c>
-      <x:c r="J2" s="12" t="str">
+      <x:c r="J2" s="29" t="str">
         <x:v>观察记录时间</x:v>
       </x:c>
-      <x:c r="K2" s="12" t="str">
+      <x:c r="K2" s="29" t="str">
         <x:v>证据状态</x:v>
       </x:c>
-      <x:c r="L2" s="12" t="str">
+      <x:c r="L2" s="29" t="str">
         <x:v>误匹配风险</x:v>
       </x:c>
-      <x:c r="M2" s="12" t="str">
+      <x:c r="M2" s="29" t="str">
         <x:v>风险门状态</x:v>
       </x:c>
-      <x:c r="N2" s="12" t="str">
+      <x:c r="N2" s="29" t="str">
         <x:v>审核人决定</x:v>
       </x:c>
-      <x:c r="O2" s="12" t="str">
+      <x:c r="O2" s="29" t="str">
         <x:v>决定日期</x:v>
       </x:c>
     </x:row>
@@ -1398,46 +1407,46 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
-      <x:c r="A2" s="12" t="str">
+      <x:c r="A2" s="29" t="str">
         <x:v>触达记录编号</x:v>
       </x:c>
-      <x:c r="B2" s="12" t="str">
+      <x:c r="B2" s="29" t="str">
         <x:v>客户编号</x:v>
       </x:c>
-      <x:c r="C2" s="12" t="str">
+      <x:c r="C2" s="29" t="str">
         <x:v>联系人编号</x:v>
       </x:c>
-      <x:c r="D2" s="12" t="str">
+      <x:c r="D2" s="29" t="str">
         <x:v>触达渠道</x:v>
       </x:c>
-      <x:c r="E2" s="12" t="str">
+      <x:c r="E2" s="29" t="str">
         <x:v>触达阶段</x:v>
       </x:c>
-      <x:c r="F2" s="12" t="str">
+      <x:c r="F2" s="29" t="str">
         <x:v>内容状态</x:v>
       </x:c>
-      <x:c r="G2" s="12" t="str">
+      <x:c r="G2" s="29" t="str">
         <x:v>计划日期</x:v>
       </x:c>
-      <x:c r="H2" s="12" t="str">
+      <x:c r="H2" s="29" t="str">
         <x:v>实际发送时间</x:v>
       </x:c>
-      <x:c r="I2" s="12" t="str">
+      <x:c r="I2" s="29" t="str">
         <x:v>实发内容或本地引用</x:v>
       </x:c>
-      <x:c r="J2" s="12" t="str">
+      <x:c r="J2" s="29" t="str">
         <x:v>回复状态</x:v>
       </x:c>
-      <x:c r="K2" s="12" t="str">
+      <x:c r="K2" s="29" t="str">
         <x:v>回复时间</x:v>
       </x:c>
-      <x:c r="L2" s="12" t="str">
+      <x:c r="L2" s="29" t="str">
         <x:v>下一步行动</x:v>
       </x:c>
-      <x:c r="M2" s="12" t="str">
+      <x:c r="M2" s="29" t="str">
         <x:v>下一步行动日期</x:v>
       </x:c>
-      <x:c r="N2" s="12" t="str">
+      <x:c r="N2" s="29" t="str">
         <x:v>业务员批准状态</x:v>
       </x:c>
     </x:row>
@@ -1509,40 +1518,40 @@
       </x:c>
     </x:row>
     <x:row r="2" ht="42" customHeight="1">
-      <x:c r="A2" s="12" t="str">
+      <x:c r="A2" s="29" t="str">
         <x:v>移交记录编号</x:v>
       </x:c>
-      <x:c r="B2" s="12" t="str">
+      <x:c r="B2" s="29" t="str">
         <x:v>客户编号</x:v>
       </x:c>
-      <x:c r="C2" s="12" t="str">
+      <x:c r="C2" s="29" t="str">
         <x:v>触发渠道</x:v>
       </x:c>
-      <x:c r="D2" s="12" t="str">
+      <x:c r="D2" s="29" t="str">
         <x:v>触发触达记录编号</x:v>
       </x:c>
-      <x:c r="E2" s="12" t="str">
+      <x:c r="E2" s="29" t="str">
         <x:v>回复内容引用</x:v>
       </x:c>
-      <x:c r="F2" s="12" t="str">
+      <x:c r="F2" s="29" t="str">
         <x:v>客户开发快照引用</x:v>
       </x:c>
-      <x:c r="G2" s="12" t="str">
+      <x:c r="G2" s="29" t="str">
         <x:v>未解决问题</x:v>
       </x:c>
-      <x:c r="H2" s="12" t="str">
+      <x:c r="H2" s="29" t="str">
         <x:v>风险门状态</x:v>
       </x:c>
-      <x:c r="I2" s="12" t="str">
+      <x:c r="I2" s="29" t="str">
         <x:v>目标技能</x:v>
       </x:c>
-      <x:c r="J2" s="12" t="str">
+      <x:c r="J2" s="29" t="str">
         <x:v>移交状态</x:v>
       </x:c>
-      <x:c r="K2" s="12" t="str">
+      <x:c r="K2" s="29" t="str">
         <x:v>业务员决定</x:v>
       </x:c>
-      <x:c r="L2" s="12" t="str">
+      <x:c r="L2" s="29" t="str">
         <x:v>决定日期</x:v>
       </x:c>
     </x:row>
@@ -1553,7 +1562,7 @@
       <x:formula1>"未触发,待核验,暂停待业务员审核,业务员批准继续,已关闭"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" errorStyle="stop" allowBlank="1" showErrorMessage="1" errorTitle="受控字段" error="请从下拉列表中选择有效值。" sqref="J3:J5000">
-      <x:formula1>"未触发,触达已暂停,待邮件助手,已移交,业务员已决定"</x:formula1>
+      <x:formula1>"未触发,待邮件助手,已移交,业务员已决定"</x:formula1>
     </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
